--- a/ghg_scen1.xlsx
+++ b/ghg_scen1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7767ba86a98102bc/TEP4290/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5885F49E-BCF2-406A-960D-1263DDCCE1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{55D822CF-3ED6-456D-8980-2715ED80C857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F367BB2-56F0-4784-A75A-BE08ACC3E873}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{350325DE-E4E4-49B1-A932-324630C5E987}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
   <si>
     <t>EPD reference</t>
   </si>
@@ -180,6 +180,24 @@
   </si>
   <si>
     <t>glass</t>
+  </si>
+  <si>
+    <t>https://www.iea.org/news/cement-technology-roadmap-plots-path-to-cutting-co2-emissions-24-by-2050</t>
+  </si>
+  <si>
+    <t>https://www.iea.org/energy-system/industry/steel</t>
+  </si>
+  <si>
+    <t>https://www.ribaj.com/intelligence/low-carbon-bricks-tackle-climate-recycled-waste-cement-free-binders/</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>https://interestingengineering.com/energy/uk-worlds-first-hydrogen-fired-brick-kiln</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S009813542500331X</t>
   </si>
 </sst>
 </file>
@@ -275,6 +293,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -594,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9CD0162-DB77-4DD0-ABD8-A57604E8F6DA}">
-  <dimension ref="C6:K29"/>
+  <dimension ref="C6:L30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="5" max="5" width="18.1328125" customWidth="1"/>
@@ -606,7 +628,7 @@
     <col min="11" max="11" width="12.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="3:11" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="6" spans="3:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="D6" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="3:11" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="7" spans="3:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
@@ -660,11 +682,14 @@
         <v>8</v>
       </c>
       <c r="K7" s="3">
-        <f>H9-(0.206*83/100)</f>
-        <v>3.5501150000000009E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="3:11" ht="15.75" x14ac:dyDescent="0.5">
+        <f>H9-(0.206*24/100)</f>
+        <v>0.15704115000000002</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="3:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C8" s="4"/>
       <c r="D8" t="s">
         <v>9</v>
@@ -692,8 +717,11 @@
         <f>H12-(0.19*32/100)</f>
         <v>0.12893499999999999</v>
       </c>
-    </row>
-    <row r="9" spans="3:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="L8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="3:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C9" s="6" t="s">
         <v>15</v>
       </c>
@@ -709,7 +737,7 @@
         <v>5.5150270999999987E-2</v>
       </c>
     </row>
-    <row r="10" spans="3:11" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="10" spans="3:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C10" s="1" t="s">
         <v>14</v>
       </c>
@@ -737,11 +765,14 @@
         <v>20</v>
       </c>
       <c r="K10" s="5">
-        <f>H18-(1.11*90/100)</f>
-        <v>0.10644999999999993</v>
-      </c>
-    </row>
-    <row r="11" spans="3:11" ht="15.75" x14ac:dyDescent="0.5">
+        <f>H18-(1.11*50/100)</f>
+        <v>0.55044999999999999</v>
+      </c>
+      <c r="L10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="3:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C11" s="4"/>
       <c r="D11" t="s">
         <v>21</v>
@@ -770,8 +801,11 @@
         <f>H21-(2.65*50/100)</f>
         <v>1.3251999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="3:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="L11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="3:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C12" s="6" t="s">
         <v>15</v>
       </c>
@@ -784,10 +818,10 @@
       </c>
       <c r="K12" s="9">
         <f>H27</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="3:11" ht="15.75" x14ac:dyDescent="0.5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="3:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
@@ -819,7 +853,7 @@
         <v>3.43946</v>
       </c>
     </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="3:12" x14ac:dyDescent="0.45">
       <c r="C14" s="4"/>
       <c r="D14" t="s">
         <v>28</v>
@@ -842,7 +876,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="3:11" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="15" spans="3:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C15" s="6" t="s">
         <v>15</v>
       </c>
@@ -851,7 +885,7 @@
         <v>-5.9422298645000007</v>
       </c>
     </row>
-    <row r="16" spans="3:11" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="16" spans="3:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C16" s="1" t="s">
         <v>20</v>
       </c>
@@ -1050,7 +1084,8 @@
         <v>42</v>
       </c>
       <c r="H27">
-        <v>4</v>
+        <f>10-(10*0.4)</f>
+        <v>6</v>
       </c>
       <c r="I27" t="s">
         <v>43</v>
@@ -1076,6 +1111,14 @@
       </c>
       <c r="I29" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.45">
+      <c r="G30" t="s">
+        <v>51</v>
+      </c>
+      <c r="I30" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/ghg_scen1.xlsx
+++ b/ghg_scen1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7767ba86a98102bc/TEP4290/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{55D822CF-3ED6-456D-8980-2715ED80C857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F367BB2-56F0-4784-A75A-BE08ACC3E873}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{55D822CF-3ED6-456D-8980-2715ED80C857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0BA5900-74D0-42C5-BEAB-DF92907299DE}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{350325DE-E4E4-49B1-A932-324630C5E987}"/>
   </bookViews>
@@ -208,7 +208,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,6 +236,14 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -254,10 +262,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -278,8 +287,10 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperkobling" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -293,10 +304,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -685,7 +692,7 @@
         <f>H9-(0.206*24/100)</f>
         <v>0.15704115000000002</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="12" t="s">
         <v>48</v>
       </c>
     </row>
@@ -717,7 +724,7 @@
         <f>H12-(0.19*32/100)</f>
         <v>0.12893499999999999</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="12" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1117,11 +1124,16 @@
       <c r="G30" t="s">
         <v>51</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="12" t="s">
         <v>52</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="L7" r:id="rId1" xr:uid="{47E7584B-1A8C-411C-9746-3DB9634595F8}"/>
+    <hyperlink ref="L8" r:id="rId2" xr:uid="{786DC17E-4439-4BDA-8CC8-226A478F084E}"/>
+    <hyperlink ref="I30" r:id="rId3" xr:uid="{51E02A2B-7018-409C-A967-8F88C3F8A3CB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>